--- a/begunici/app_types/animals/excel_templates/archive_acts/prodaja.xlsx
+++ b/begunici/app_types/animals/excel_templates/archive_acts/prodaja.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim\Desktop\begunici\begunici\app_types\animals\excel_templates\archive_acts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{80F90B5F-28AE-47A9-8613-E354DB2AF8B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5A44AF-D3D0-4082-A634-BB5C9ED990B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{53909B8C-51F5-44CE-B125-47A20653857F}"/>
   </bookViews>
@@ -160,12 +160,12 @@
     <t>г.</t>
   </si>
   <si>
-    <t>ООО "Бегуницы"</t>
-  </si>
-  <si>
     <t>Воз-
 раст,
 мес.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ООО "Ферма "Бегуницы"												</t>
   </si>
 </sst>
 </file>
@@ -786,7 +786,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -800,12 +800,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="16" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="24" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="24" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -817,6 +811,204 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="24" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="10" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="10" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="10" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="10" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="10" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="10" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="14" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="12" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="15" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="6" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="13" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="6" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="6" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="9" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="9" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="10" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="11" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="4" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="7" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="22" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="21" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="23" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="20" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="20" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="20" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="17" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="8" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="18" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="19" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="24" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -824,208 +1016,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="13" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="13" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="23" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="17" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="8" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="18" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="19" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="22" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="21" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="20" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="20" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="20" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="4" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="7" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="9" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="9" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="10" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="11" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="6" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="6" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="6" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="12" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="15" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="10" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="10" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="10" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="10" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="10" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="10" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="14" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="25">
@@ -1083,8 +1074,8 @@
       <xdr:row>34</xdr:row>
       <xdr:rowOff>95460</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="2" name="Рукописный ввод 1">
@@ -1103,7 +1094,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="2" name="Рукописный ввод 1">
@@ -1502,1104 +1493,1067 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="17"/>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-      <c r="AF1" s="17"/>
-      <c r="AK1" s="18" t="s">
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="20"/>
+      <c r="Z1" s="20"/>
+      <c r="AA1" s="20"/>
+      <c r="AB1" s="20"/>
+      <c r="AC1" s="20"/>
+      <c r="AD1" s="20"/>
+      <c r="AE1" s="20"/>
+      <c r="AF1" s="20"/>
+      <c r="AK1" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="AL1" s="17"/>
-      <c r="AM1" s="17"/>
-      <c r="AN1" s="17"/>
-      <c r="AO1" s="17"/>
-      <c r="AP1" s="17"/>
-      <c r="AQ1" s="17"/>
-      <c r="AR1" s="17"/>
+      <c r="AL1" s="20"/>
+      <c r="AM1" s="20"/>
+      <c r="AN1" s="20"/>
+      <c r="AO1" s="20"/>
+      <c r="AP1" s="20"/>
+      <c r="AQ1" s="20"/>
+      <c r="AR1" s="20"/>
     </row>
     <row r="2" spans="1:44" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="17"/>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="17"/>
-      <c r="S2" s="17"/>
-      <c r="T2" s="17"/>
-      <c r="U2" s="17"/>
-      <c r="V2" s="17"/>
-      <c r="W2" s="17"/>
-      <c r="X2" s="17"/>
-      <c r="Y2" s="17"/>
-      <c r="Z2" s="17"/>
-      <c r="AA2" s="17"/>
-      <c r="AB2" s="17"/>
-      <c r="AC2" s="17"/>
-      <c r="AD2" s="17"/>
-      <c r="AE2" s="17"/>
-      <c r="AF2" s="17"/>
-      <c r="AK2" s="17"/>
-      <c r="AL2" s="17"/>
-      <c r="AM2" s="17"/>
-      <c r="AN2" s="17"/>
-      <c r="AO2" s="17"/>
-      <c r="AP2" s="17"/>
-      <c r="AQ2" s="17"/>
-      <c r="AR2" s="17"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
+      <c r="V2" s="20"/>
+      <c r="W2" s="20"/>
+      <c r="X2" s="20"/>
+      <c r="Y2" s="20"/>
+      <c r="Z2" s="20"/>
+      <c r="AA2" s="20"/>
+      <c r="AB2" s="20"/>
+      <c r="AC2" s="20"/>
+      <c r="AD2" s="20"/>
+      <c r="AE2" s="20"/>
+      <c r="AF2" s="20"/>
+      <c r="AK2" s="20"/>
+      <c r="AL2" s="20"/>
+      <c r="AM2" s="20"/>
+      <c r="AN2" s="20"/>
+      <c r="AO2" s="20"/>
+      <c r="AP2" s="20"/>
+      <c r="AQ2" s="20"/>
+      <c r="AR2" s="20"/>
     </row>
     <row r="3" spans="1:44" ht="2.85" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
-      <c r="N3" s="19"/>
-      <c r="O3" s="19"/>
-      <c r="P3" s="19"/>
-      <c r="Q3" s="19"/>
-      <c r="R3" s="19"/>
-      <c r="S3" s="19"/>
-      <c r="T3" s="19"/>
-      <c r="U3" s="19"/>
-      <c r="V3" s="19"/>
-      <c r="W3" s="19"/>
-      <c r="X3" s="19"/>
-      <c r="Y3" s="19"/>
-      <c r="Z3" s="19"/>
-      <c r="AA3" s="19"/>
-      <c r="AB3" s="19"/>
-      <c r="AC3" s="19"/>
-      <c r="AD3" s="19"/>
-      <c r="AE3" s="19"/>
-      <c r="AF3" s="19"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="67"/>
+      <c r="M3" s="67"/>
+      <c r="N3" s="67"/>
+      <c r="O3" s="67"/>
+      <c r="P3" s="67"/>
+      <c r="Q3" s="67"/>
+      <c r="R3" s="67"/>
+      <c r="S3" s="67"/>
+      <c r="T3" s="67"/>
+      <c r="U3" s="67"/>
+      <c r="V3" s="67"/>
+      <c r="W3" s="67"/>
+      <c r="X3" s="67"/>
+      <c r="Y3" s="67"/>
+      <c r="Z3" s="67"/>
+      <c r="AA3" s="67"/>
+      <c r="AB3" s="67"/>
+      <c r="AC3" s="67"/>
+      <c r="AD3" s="67"/>
+      <c r="AE3" s="67"/>
+      <c r="AF3" s="67"/>
     </row>
     <row r="4" spans="1:44" ht="11.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="19"/>
-      <c r="S4" s="19"/>
-      <c r="T4" s="19"/>
-      <c r="U4" s="19"/>
-      <c r="V4" s="19"/>
-      <c r="W4" s="19"/>
-      <c r="X4" s="19"/>
-      <c r="Y4" s="19"/>
-      <c r="Z4" s="19"/>
-      <c r="AA4" s="19"/>
-      <c r="AB4" s="19"/>
-      <c r="AC4" s="19"/>
-      <c r="AD4" s="19"/>
-      <c r="AE4" s="19"/>
-      <c r="AF4" s="19"/>
-      <c r="AO4" s="20" t="s">
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="67"/>
+      <c r="O4" s="67"/>
+      <c r="P4" s="67"/>
+      <c r="Q4" s="67"/>
+      <c r="R4" s="67"/>
+      <c r="S4" s="67"/>
+      <c r="T4" s="67"/>
+      <c r="U4" s="67"/>
+      <c r="V4" s="67"/>
+      <c r="W4" s="67"/>
+      <c r="X4" s="67"/>
+      <c r="Y4" s="67"/>
+      <c r="Z4" s="67"/>
+      <c r="AA4" s="67"/>
+      <c r="AB4" s="67"/>
+      <c r="AC4" s="67"/>
+      <c r="AD4" s="67"/>
+      <c r="AE4" s="67"/>
+      <c r="AF4" s="67"/>
+      <c r="AO4" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="AP4" s="21"/>
-      <c r="AQ4" s="21"/>
-      <c r="AR4" s="22"/>
+      <c r="AP4" s="51"/>
+      <c r="AQ4" s="51"/>
+      <c r="AR4" s="69"/>
     </row>
     <row r="5" spans="1:44" ht="2.85" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="AO5" s="23"/>
-      <c r="AP5" s="24"/>
-      <c r="AQ5" s="24"/>
-      <c r="AR5" s="25"/>
+      <c r="AO5" s="39"/>
+      <c r="AP5" s="32"/>
+      <c r="AQ5" s="32"/>
+      <c r="AR5" s="36"/>
     </row>
     <row r="6" spans="1:44" ht="2.85" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
-      <c r="M6" s="26"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="26"/>
-      <c r="P6" s="26"/>
-      <c r="Q6" s="26"/>
-      <c r="R6" s="26"/>
-      <c r="S6" s="26"/>
-      <c r="T6" s="26"/>
-      <c r="U6" s="26"/>
-      <c r="V6" s="26"/>
-      <c r="W6" s="27" t="s">
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="70" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="70"/>
+      <c r="N6" s="70"/>
+      <c r="O6" s="70"/>
+      <c r="P6" s="70"/>
+      <c r="Q6" s="70"/>
+      <c r="R6" s="70"/>
+      <c r="S6" s="70"/>
+      <c r="T6" s="70"/>
+      <c r="U6" s="70"/>
+      <c r="V6" s="70"/>
+      <c r="W6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="X6" s="27"/>
-      <c r="Y6" s="27"/>
-      <c r="Z6" s="27"/>
-      <c r="AA6" s="27"/>
-      <c r="AB6" s="27"/>
-      <c r="AC6" s="27"/>
-      <c r="AD6" s="27"/>
-      <c r="AE6" s="27"/>
-      <c r="AF6" s="27"/>
-      <c r="AG6" s="27"/>
-      <c r="AH6" s="27"/>
-      <c r="AI6" s="27"/>
-      <c r="AJ6" s="27"/>
-      <c r="AK6" s="27"/>
-      <c r="AM6" s="18" t="s">
+      <c r="X6" s="71"/>
+      <c r="Y6" s="71"/>
+      <c r="Z6" s="71"/>
+      <c r="AA6" s="71"/>
+      <c r="AB6" s="71"/>
+      <c r="AC6" s="71"/>
+      <c r="AD6" s="71"/>
+      <c r="AE6" s="71"/>
+      <c r="AF6" s="71"/>
+      <c r="AG6" s="71"/>
+      <c r="AH6" s="71"/>
+      <c r="AI6" s="71"/>
+      <c r="AJ6" s="71"/>
+      <c r="AK6" s="71"/>
+      <c r="AM6" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="AO6" s="28" t="s">
+      <c r="AO6" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="AP6" s="29"/>
-      <c r="AQ6" s="29"/>
-      <c r="AR6" s="30"/>
+      <c r="AP6" s="30"/>
+      <c r="AQ6" s="30"/>
+      <c r="AR6" s="38"/>
     </row>
     <row r="7" spans="1:44" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
-      <c r="P7" s="26"/>
-      <c r="Q7" s="26"/>
-      <c r="R7" s="26"/>
-      <c r="S7" s="26"/>
-      <c r="T7" s="26"/>
-      <c r="U7" s="26"/>
-      <c r="V7" s="26"/>
-      <c r="W7" s="27"/>
-      <c r="X7" s="27"/>
-      <c r="Y7" s="27"/>
-      <c r="Z7" s="27"/>
-      <c r="AA7" s="27"/>
-      <c r="AB7" s="27"/>
-      <c r="AC7" s="27"/>
-      <c r="AD7" s="27"/>
-      <c r="AE7" s="27"/>
-      <c r="AF7" s="27"/>
-      <c r="AG7" s="27"/>
-      <c r="AH7" s="27"/>
-      <c r="AI7" s="27"/>
-      <c r="AJ7" s="27"/>
-      <c r="AK7" s="27"/>
-      <c r="AM7" s="17"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="70"/>
+      <c r="G7" s="70"/>
+      <c r="H7" s="70"/>
+      <c r="I7" s="70"/>
+      <c r="J7" s="70"/>
+      <c r="K7" s="70"/>
+      <c r="L7" s="70"/>
+      <c r="M7" s="70"/>
+      <c r="N7" s="70"/>
+      <c r="O7" s="70"/>
+      <c r="P7" s="70"/>
+      <c r="Q7" s="70"/>
+      <c r="R7" s="70"/>
+      <c r="S7" s="70"/>
+      <c r="T7" s="70"/>
+      <c r="U7" s="70"/>
+      <c r="V7" s="70"/>
+      <c r="W7" s="71"/>
+      <c r="X7" s="71"/>
+      <c r="Y7" s="71"/>
+      <c r="Z7" s="71"/>
+      <c r="AA7" s="71"/>
+      <c r="AB7" s="71"/>
+      <c r="AC7" s="71"/>
+      <c r="AD7" s="71"/>
+      <c r="AE7" s="71"/>
+      <c r="AF7" s="71"/>
+      <c r="AG7" s="71"/>
+      <c r="AH7" s="71"/>
+      <c r="AI7" s="71"/>
+      <c r="AJ7" s="71"/>
+      <c r="AK7" s="71"/>
+      <c r="AM7" s="20"/>
       <c r="AO7" s="31"/>
-      <c r="AP7" s="24"/>
-      <c r="AQ7" s="24"/>
-      <c r="AR7" s="32"/>
+      <c r="AP7" s="32"/>
+      <c r="AQ7" s="32"/>
+      <c r="AR7" s="40"/>
     </row>
     <row r="8" spans="1:44" ht="2.85" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="26"/>
-      <c r="R8" s="26"/>
-      <c r="S8" s="26"/>
-      <c r="T8" s="26"/>
-      <c r="U8" s="26"/>
-      <c r="V8" s="26"/>
-      <c r="W8" s="27"/>
-      <c r="X8" s="27"/>
-      <c r="Y8" s="27"/>
-      <c r="Z8" s="27"/>
-      <c r="AA8" s="27"/>
-      <c r="AB8" s="27"/>
-      <c r="AC8" s="27"/>
-      <c r="AD8" s="27"/>
-      <c r="AE8" s="27"/>
-      <c r="AF8" s="27"/>
-      <c r="AG8" s="27"/>
-      <c r="AH8" s="27"/>
-      <c r="AI8" s="27"/>
-      <c r="AJ8" s="27"/>
-      <c r="AK8" s="27"/>
-      <c r="AM8" s="17"/>
-      <c r="AO8" s="33"/>
-      <c r="AP8" s="30"/>
-      <c r="AQ8" s="36"/>
-      <c r="AR8" s="39"/>
+      <c r="A8" s="26"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="70"/>
+      <c r="J8" s="70"/>
+      <c r="K8" s="70"/>
+      <c r="L8" s="70"/>
+      <c r="M8" s="70"/>
+      <c r="N8" s="70"/>
+      <c r="O8" s="70"/>
+      <c r="P8" s="70"/>
+      <c r="Q8" s="70"/>
+      <c r="R8" s="70"/>
+      <c r="S8" s="70"/>
+      <c r="T8" s="70"/>
+      <c r="U8" s="70"/>
+      <c r="V8" s="70"/>
+      <c r="W8" s="71"/>
+      <c r="X8" s="71"/>
+      <c r="Y8" s="71"/>
+      <c r="Z8" s="71"/>
+      <c r="AA8" s="71"/>
+      <c r="AB8" s="71"/>
+      <c r="AC8" s="71"/>
+      <c r="AD8" s="71"/>
+      <c r="AE8" s="71"/>
+      <c r="AF8" s="71"/>
+      <c r="AG8" s="71"/>
+      <c r="AH8" s="71"/>
+      <c r="AI8" s="71"/>
+      <c r="AJ8" s="71"/>
+      <c r="AK8" s="71"/>
+      <c r="AM8" s="20"/>
+      <c r="AO8" s="73"/>
+      <c r="AP8" s="38"/>
+      <c r="AQ8" s="53"/>
+      <c r="AR8" s="55"/>
     </row>
     <row r="9" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="6"/>
-      <c r="T9" s="6"/>
-      <c r="U9" s="6"/>
-      <c r="V9" s="6"/>
-      <c r="W9" s="6"/>
-      <c r="X9" s="6"/>
-      <c r="AM9" s="18" t="s">
+      <c r="AM9" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="AO9" s="34"/>
-      <c r="AP9" s="35"/>
-      <c r="AQ9" s="37"/>
-      <c r="AR9" s="40"/>
+      <c r="AO9" s="74"/>
+      <c r="AP9" s="75"/>
+      <c r="AQ9" s="54"/>
+      <c r="AR9" s="56"/>
     </row>
     <row r="10" spans="1:44" ht="5.85" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="15"/>
-      <c r="O10" s="15"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="15"/>
-      <c r="S10" s="15"/>
-      <c r="T10" s="15"/>
-      <c r="U10" s="15"/>
-      <c r="V10" s="15"/>
-      <c r="W10" s="15"/>
-      <c r="X10" s="15"/>
-      <c r="AM10" s="17"/>
+      <c r="B10" s="78"/>
+      <c r="C10" s="78"/>
+      <c r="D10" s="78"/>
+      <c r="E10" s="78"/>
+      <c r="F10" s="78"/>
+      <c r="G10" s="78"/>
+      <c r="H10" s="78"/>
+      <c r="I10" s="78"/>
+      <c r="J10" s="78"/>
+      <c r="K10" s="78"/>
+      <c r="L10" s="78"/>
+      <c r="M10" s="78"/>
+      <c r="N10" s="78"/>
+      <c r="O10" s="78"/>
+      <c r="P10" s="78"/>
+      <c r="Q10" s="78"/>
+      <c r="R10" s="78"/>
+      <c r="S10" s="78"/>
+      <c r="T10" s="78"/>
+      <c r="U10" s="78"/>
+      <c r="V10" s="78"/>
+      <c r="W10" s="78"/>
+      <c r="X10" s="78"/>
+      <c r="AM10" s="20"/>
       <c r="AO10" s="31"/>
-      <c r="AP10" s="32"/>
-      <c r="AQ10" s="38"/>
-      <c r="AR10" s="41"/>
+      <c r="AP10" s="40"/>
+      <c r="AQ10" s="28"/>
+      <c r="AR10" s="57"/>
     </row>
     <row r="11" spans="1:44" ht="16.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="15"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-      <c r="O11" s="15"/>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="15"/>
-      <c r="S11" s="15"/>
-      <c r="T11" s="15"/>
-      <c r="U11" s="15"/>
-      <c r="V11" s="15"/>
-      <c r="W11" s="15"/>
-      <c r="X11" s="15"/>
-      <c r="AM11" s="17"/>
-      <c r="AO11" s="42" t="s">
+      <c r="A11" s="78"/>
+      <c r="B11" s="78"/>
+      <c r="C11" s="78"/>
+      <c r="D11" s="78"/>
+      <c r="E11" s="78"/>
+      <c r="F11" s="78"/>
+      <c r="G11" s="78"/>
+      <c r="H11" s="78"/>
+      <c r="I11" s="78"/>
+      <c r="J11" s="78"/>
+      <c r="K11" s="78"/>
+      <c r="L11" s="78"/>
+      <c r="M11" s="78"/>
+      <c r="N11" s="78"/>
+      <c r="O11" s="78"/>
+      <c r="P11" s="78"/>
+      <c r="Q11" s="78"/>
+      <c r="R11" s="78"/>
+      <c r="S11" s="78"/>
+      <c r="T11" s="78"/>
+      <c r="U11" s="78"/>
+      <c r="V11" s="78"/>
+      <c r="W11" s="78"/>
+      <c r="X11" s="78"/>
+      <c r="AM11" s="20"/>
+      <c r="AO11" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="AP11" s="29"/>
-      <c r="AQ11" s="29"/>
-      <c r="AR11" s="30"/>
+      <c r="AP11" s="30"/>
+      <c r="AQ11" s="30"/>
+      <c r="AR11" s="38"/>
     </row>
     <row r="12" spans="1:44" ht="5.85" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="43"/>
-      <c r="L12" s="43"/>
-      <c r="M12" s="43"/>
-      <c r="N12" s="43"/>
-      <c r="O12" s="43"/>
-      <c r="P12" s="43"/>
-      <c r="Q12" s="43"/>
-      <c r="R12" s="43"/>
-      <c r="S12" s="43"/>
-      <c r="T12" s="43"/>
-      <c r="U12" s="43"/>
-      <c r="V12" s="43"/>
-      <c r="W12" s="43"/>
-      <c r="X12" s="43"/>
-      <c r="AM12" s="18" t="s">
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="60"/>
+      <c r="L12" s="60"/>
+      <c r="M12" s="60"/>
+      <c r="N12" s="60"/>
+      <c r="O12" s="60"/>
+      <c r="P12" s="60"/>
+      <c r="Q12" s="60"/>
+      <c r="R12" s="60"/>
+      <c r="S12" s="60"/>
+      <c r="T12" s="60"/>
+      <c r="U12" s="60"/>
+      <c r="V12" s="60"/>
+      <c r="W12" s="60"/>
+      <c r="X12" s="60"/>
+      <c r="AM12" s="58" t="s">
         <v>11</v>
       </c>
       <c r="AO12" s="31"/>
-      <c r="AP12" s="24"/>
-      <c r="AQ12" s="24"/>
-      <c r="AR12" s="32"/>
+      <c r="AP12" s="32"/>
+      <c r="AQ12" s="32"/>
+      <c r="AR12" s="40"/>
     </row>
     <row r="13" spans="1:44" ht="5.85" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="43"/>
-      <c r="M13" s="43"/>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="43"/>
-      <c r="T13" s="43"/>
-      <c r="U13" s="43"/>
-      <c r="V13" s="43"/>
-      <c r="W13" s="43"/>
-      <c r="X13" s="43"/>
-      <c r="AM13" s="17"/>
-      <c r="AO13" s="44" t="s">
+      <c r="A13" s="26"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="60"/>
+      <c r="K13" s="60"/>
+      <c r="L13" s="60"/>
+      <c r="M13" s="60"/>
+      <c r="N13" s="60"/>
+      <c r="O13" s="60"/>
+      <c r="P13" s="60"/>
+      <c r="Q13" s="60"/>
+      <c r="R13" s="60"/>
+      <c r="S13" s="60"/>
+      <c r="T13" s="60"/>
+      <c r="U13" s="60"/>
+      <c r="V13" s="60"/>
+      <c r="W13" s="60"/>
+      <c r="X13" s="60"/>
+      <c r="AM13" s="20"/>
+      <c r="AO13" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="AP13" s="29"/>
-      <c r="AQ13" s="29"/>
-      <c r="AR13" s="45"/>
+      <c r="AP13" s="30"/>
+      <c r="AQ13" s="30"/>
+      <c r="AR13" s="35"/>
     </row>
     <row r="14" spans="1:44" ht="2.85" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="43"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="O14" s="43"/>
-      <c r="P14" s="43"/>
-      <c r="Q14" s="43"/>
-      <c r="R14" s="43"/>
-      <c r="S14" s="43"/>
-      <c r="T14" s="43"/>
-      <c r="U14" s="43"/>
-      <c r="V14" s="43"/>
-      <c r="W14" s="43"/>
-      <c r="X14" s="43"/>
-      <c r="AM14" s="17"/>
-      <c r="AO14" s="46"/>
-      <c r="AP14" s="17"/>
-      <c r="AQ14" s="17"/>
-      <c r="AR14" s="47"/>
+      <c r="A14" s="26"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="60"/>
+      <c r="K14" s="60"/>
+      <c r="L14" s="60"/>
+      <c r="M14" s="60"/>
+      <c r="N14" s="60"/>
+      <c r="O14" s="60"/>
+      <c r="P14" s="60"/>
+      <c r="Q14" s="60"/>
+      <c r="R14" s="60"/>
+      <c r="S14" s="60"/>
+      <c r="T14" s="60"/>
+      <c r="U14" s="60"/>
+      <c r="V14" s="60"/>
+      <c r="W14" s="60"/>
+      <c r="X14" s="60"/>
+      <c r="AM14" s="20"/>
+      <c r="AO14" s="62"/>
+      <c r="AP14" s="20"/>
+      <c r="AQ14" s="20"/>
+      <c r="AR14" s="63"/>
     </row>
     <row r="15" spans="1:44" ht="2.85" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="48"/>
-      <c r="K15" s="48"/>
-      <c r="L15" s="48"/>
-      <c r="M15" s="48"/>
-      <c r="N15" s="48"/>
-      <c r="O15" s="48"/>
-      <c r="P15" s="48"/>
-      <c r="Q15" s="48"/>
-      <c r="R15" s="48"/>
-      <c r="S15" s="48"/>
-      <c r="T15" s="48"/>
-      <c r="U15" s="48"/>
-      <c r="V15" s="48"/>
-      <c r="W15" s="48"/>
-      <c r="X15" s="48"/>
-      <c r="AO15" s="23"/>
-      <c r="AP15" s="24"/>
-      <c r="AQ15" s="24"/>
-      <c r="AR15" s="25"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
+      <c r="H15" s="64"/>
+      <c r="I15" s="64"/>
+      <c r="J15" s="64"/>
+      <c r="K15" s="64"/>
+      <c r="L15" s="64"/>
+      <c r="M15" s="64"/>
+      <c r="N15" s="64"/>
+      <c r="O15" s="64"/>
+      <c r="P15" s="64"/>
+      <c r="Q15" s="64"/>
+      <c r="R15" s="64"/>
+      <c r="S15" s="64"/>
+      <c r="T15" s="64"/>
+      <c r="U15" s="64"/>
+      <c r="V15" s="64"/>
+      <c r="W15" s="64"/>
+      <c r="X15" s="64"/>
+      <c r="AO15" s="39"/>
+      <c r="AP15" s="32"/>
+      <c r="AQ15" s="32"/>
+      <c r="AR15" s="36"/>
     </row>
     <row r="16" spans="1:44" ht="11.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="48"/>
-      <c r="I16" s="48"/>
-      <c r="J16" s="48"/>
-      <c r="K16" s="48"/>
-      <c r="L16" s="48"/>
-      <c r="M16" s="48"/>
-      <c r="N16" s="48"/>
-      <c r="O16" s="48"/>
-      <c r="P16" s="48"/>
-      <c r="Q16" s="48"/>
-      <c r="R16" s="48"/>
-      <c r="S16" s="48"/>
-      <c r="T16" s="48"/>
-      <c r="U16" s="48"/>
-      <c r="V16" s="48"/>
-      <c r="W16" s="48"/>
-      <c r="X16" s="48"/>
-      <c r="AO16" s="49" t="s">
+      <c r="A16" s="26"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="64"/>
+      <c r="G16" s="64"/>
+      <c r="H16" s="64"/>
+      <c r="I16" s="64"/>
+      <c r="J16" s="64"/>
+      <c r="K16" s="64"/>
+      <c r="L16" s="64"/>
+      <c r="M16" s="64"/>
+      <c r="N16" s="64"/>
+      <c r="O16" s="64"/>
+      <c r="P16" s="64"/>
+      <c r="Q16" s="64"/>
+      <c r="R16" s="64"/>
+      <c r="S16" s="64"/>
+      <c r="T16" s="64"/>
+      <c r="U16" s="64"/>
+      <c r="V16" s="64"/>
+      <c r="W16" s="64"/>
+      <c r="X16" s="64"/>
+      <c r="AO16" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="AP16" s="50"/>
-      <c r="AQ16" s="50"/>
-      <c r="AR16" s="51"/>
+      <c r="AP16" s="22"/>
+      <c r="AQ16" s="22"/>
+      <c r="AR16" s="23"/>
     </row>
     <row r="17" spans="1:44" ht="11.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="52"/>
-      <c r="G17" s="52"/>
-      <c r="H17" s="52"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="52"/>
-      <c r="K17" s="52"/>
-      <c r="L17" s="52"/>
-      <c r="M17" s="52"/>
-      <c r="N17" s="52"/>
-      <c r="O17" s="52"/>
-      <c r="P17" s="52"/>
-      <c r="Q17" s="52"/>
-      <c r="R17" s="52"/>
-      <c r="S17" s="52"/>
-      <c r="T17" s="52"/>
-      <c r="U17" s="52"/>
-      <c r="V17" s="52"/>
-      <c r="W17" s="52"/>
-      <c r="X17" s="52"/>
-      <c r="AO17" s="53" t="s">
+      <c r="B17" s="26"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="64"/>
+      <c r="G17" s="64"/>
+      <c r="H17" s="64"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="64"/>
+      <c r="K17" s="64"/>
+      <c r="L17" s="64"/>
+      <c r="M17" s="64"/>
+      <c r="N17" s="64"/>
+      <c r="O17" s="64"/>
+      <c r="P17" s="64"/>
+      <c r="Q17" s="64"/>
+      <c r="R17" s="64"/>
+      <c r="S17" s="64"/>
+      <c r="T17" s="64"/>
+      <c r="U17" s="64"/>
+      <c r="V17" s="64"/>
+      <c r="W17" s="64"/>
+      <c r="X17" s="64"/>
+      <c r="AO17" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="AP17" s="50"/>
-      <c r="AQ17" s="50"/>
-      <c r="AR17" s="54"/>
+      <c r="AP17" s="22"/>
+      <c r="AQ17" s="22"/>
+      <c r="AR17" s="46"/>
     </row>
     <row r="18" spans="1:44" ht="2.85" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="52"/>
-      <c r="G18" s="52"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="52"/>
-      <c r="K18" s="52"/>
-      <c r="L18" s="52"/>
-      <c r="M18" s="52"/>
-      <c r="N18" s="52"/>
-      <c r="O18" s="52"/>
-      <c r="P18" s="52"/>
-      <c r="Q18" s="52"/>
-      <c r="R18" s="52"/>
-      <c r="S18" s="52"/>
-      <c r="T18" s="52"/>
-      <c r="U18" s="52"/>
-      <c r="V18" s="52"/>
-      <c r="W18" s="52"/>
-      <c r="X18" s="52"/>
+      <c r="A18" s="26"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="64"/>
+      <c r="G18" s="64"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="64"/>
+      <c r="J18" s="64"/>
+      <c r="K18" s="64"/>
+      <c r="L18" s="64"/>
+      <c r="M18" s="64"/>
+      <c r="N18" s="64"/>
+      <c r="O18" s="64"/>
+      <c r="P18" s="64"/>
+      <c r="Q18" s="64"/>
+      <c r="R18" s="64"/>
+      <c r="S18" s="64"/>
+      <c r="T18" s="64"/>
+      <c r="U18" s="64"/>
+      <c r="V18" s="64"/>
+      <c r="W18" s="64"/>
+      <c r="X18" s="64"/>
     </row>
     <row r="19" spans="1:44" ht="86.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="59" t="s">
+      <c r="A19" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="51"/>
-      <c r="C19" s="55" t="s">
+      <c r="B19" s="23"/>
+      <c r="C19" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="56"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="56"/>
-      <c r="H19" s="56"/>
-      <c r="I19" s="57"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="25"/>
       <c r="J19" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L19" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="L19" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="M19" s="50"/>
-      <c r="N19" s="51"/>
-      <c r="O19" s="55" t="s">
+      <c r="M19" s="22"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="P19" s="56"/>
-      <c r="Q19" s="56"/>
-      <c r="R19" s="57"/>
-      <c r="S19" s="59" t="s">
+      <c r="P19" s="48"/>
+      <c r="Q19" s="48"/>
+      <c r="R19" s="25"/>
+      <c r="S19" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="T19" s="51"/>
-      <c r="U19" s="55" t="s">
+      <c r="T19" s="23"/>
+      <c r="U19" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="V19" s="56"/>
-      <c r="W19" s="57"/>
-      <c r="X19" s="70" t="s">
+      <c r="V19" s="48"/>
+      <c r="W19" s="25"/>
+      <c r="X19" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="Y19" s="51"/>
+      <c r="Y19" s="23"/>
       <c r="Z19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AA19" s="59" t="s">
+      <c r="AA19" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="AB19" s="50"/>
-      <c r="AC19" s="50"/>
-      <c r="AD19" s="50"/>
-      <c r="AE19" s="50"/>
-      <c r="AF19" s="50"/>
-      <c r="AG19" s="50"/>
-      <c r="AH19" s="51"/>
-      <c r="AI19" s="60" t="s">
+      <c r="AB19" s="22"/>
+      <c r="AC19" s="22"/>
+      <c r="AD19" s="22"/>
+      <c r="AE19" s="22"/>
+      <c r="AF19" s="22"/>
+      <c r="AG19" s="22"/>
+      <c r="AH19" s="23"/>
+      <c r="AI19" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="AJ19" s="21"/>
-      <c r="AK19" s="21"/>
-      <c r="AL19" s="21"/>
-      <c r="AM19" s="21"/>
-      <c r="AN19" s="21"/>
-      <c r="AO19" s="61"/>
-      <c r="AP19" s="59" t="s">
+      <c r="AJ19" s="51"/>
+      <c r="AK19" s="51"/>
+      <c r="AL19" s="51"/>
+      <c r="AM19" s="51"/>
+      <c r="AN19" s="51"/>
+      <c r="AO19" s="52"/>
+      <c r="AP19" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="AQ19" s="50"/>
-      <c r="AR19" s="51"/>
+      <c r="AQ19" s="22"/>
+      <c r="AR19" s="23"/>
     </row>
     <row r="20" spans="1:44" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="63"/>
-      <c r="B20" s="30"/>
-      <c r="C20" s="64"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="65"/>
-      <c r="K20" s="66"/>
-      <c r="L20" s="67"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="30"/>
-      <c r="O20" s="67"/>
-      <c r="P20" s="29"/>
-      <c r="Q20" s="29"/>
-      <c r="R20" s="30"/>
-      <c r="S20" s="67"/>
-      <c r="T20" s="30"/>
-      <c r="U20" s="67"/>
-      <c r="V20" s="29"/>
-      <c r="W20" s="30"/>
-      <c r="X20" s="67"/>
-      <c r="Y20" s="30"/>
-      <c r="Z20" s="66"/>
-      <c r="AA20" s="67"/>
-      <c r="AB20" s="29"/>
-      <c r="AC20" s="29"/>
-      <c r="AD20" s="29"/>
-      <c r="AE20" s="29"/>
-      <c r="AF20" s="29"/>
-      <c r="AG20" s="29"/>
-      <c r="AH20" s="29"/>
-      <c r="AI20" s="75"/>
-      <c r="AJ20" s="76"/>
-      <c r="AK20" s="76"/>
-      <c r="AL20" s="76"/>
-      <c r="AM20" s="76"/>
-      <c r="AN20" s="76"/>
-      <c r="AO20" s="77"/>
-      <c r="AP20" s="62" t="s">
+      <c r="A20" s="37"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="27"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="38"/>
+      <c r="O20" s="29"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="38"/>
+      <c r="S20" s="29"/>
+      <c r="T20" s="38"/>
+      <c r="U20" s="29"/>
+      <c r="V20" s="30"/>
+      <c r="W20" s="38"/>
+      <c r="X20" s="29"/>
+      <c r="Y20" s="38"/>
+      <c r="Z20" s="27"/>
+      <c r="AA20" s="29"/>
+      <c r="AB20" s="30"/>
+      <c r="AC20" s="30"/>
+      <c r="AD20" s="30"/>
+      <c r="AE20" s="30"/>
+      <c r="AF20" s="30"/>
+      <c r="AG20" s="30"/>
+      <c r="AH20" s="30"/>
+      <c r="AI20" s="10"/>
+      <c r="AJ20" s="11"/>
+      <c r="AK20" s="11"/>
+      <c r="AL20" s="11"/>
+      <c r="AM20" s="11"/>
+      <c r="AN20" s="11"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="AQ20" s="29"/>
-      <c r="AR20" s="45"/>
+      <c r="AQ20" s="30"/>
+      <c r="AR20" s="35"/>
     </row>
     <row r="21" spans="1:44" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="23"/>
-      <c r="B21" s="32"/>
+      <c r="A21" s="39"/>
+      <c r="B21" s="40"/>
       <c r="C21" s="31"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="38"/>
-      <c r="K21" s="38"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="28"/>
       <c r="L21" s="31"/>
-      <c r="M21" s="24"/>
-      <c r="N21" s="32"/>
+      <c r="M21" s="32"/>
+      <c r="N21" s="40"/>
       <c r="O21" s="31"/>
-      <c r="P21" s="24"/>
-      <c r="Q21" s="24"/>
-      <c r="R21" s="32"/>
-      <c r="S21" s="68"/>
-      <c r="T21" s="69"/>
+      <c r="P21" s="32"/>
+      <c r="Q21" s="32"/>
+      <c r="R21" s="40"/>
+      <c r="S21" s="43"/>
+      <c r="T21" s="44"/>
       <c r="U21" s="31"/>
-      <c r="V21" s="24"/>
-      <c r="W21" s="32"/>
+      <c r="V21" s="32"/>
+      <c r="W21" s="40"/>
       <c r="X21" s="31"/>
-      <c r="Y21" s="32"/>
-      <c r="Z21" s="38"/>
+      <c r="Y21" s="40"/>
+      <c r="Z21" s="28"/>
       <c r="AA21" s="31"/>
-      <c r="AB21" s="24"/>
-      <c r="AC21" s="24"/>
-      <c r="AD21" s="24"/>
-      <c r="AE21" s="24"/>
-      <c r="AF21" s="24"/>
-      <c r="AG21" s="24"/>
-      <c r="AH21" s="24"/>
-      <c r="AI21" s="78"/>
-      <c r="AJ21" s="79"/>
-      <c r="AK21" s="79"/>
-      <c r="AL21" s="79"/>
-      <c r="AM21" s="79"/>
-      <c r="AN21" s="79"/>
-      <c r="AO21" s="80"/>
-      <c r="AP21" s="24"/>
-      <c r="AQ21" s="24"/>
-      <c r="AR21" s="25"/>
+      <c r="AB21" s="32"/>
+      <c r="AC21" s="32"/>
+      <c r="AD21" s="32"/>
+      <c r="AE21" s="32"/>
+      <c r="AF21" s="32"/>
+      <c r="AG21" s="32"/>
+      <c r="AH21" s="32"/>
+      <c r="AI21" s="13"/>
+      <c r="AJ21" s="14"/>
+      <c r="AK21" s="14"/>
+      <c r="AL21" s="14"/>
+      <c r="AM21" s="14"/>
+      <c r="AN21" s="14"/>
+      <c r="AO21" s="15"/>
+      <c r="AP21" s="32"/>
+      <c r="AQ21" s="32"/>
+      <c r="AR21" s="36"/>
     </row>
     <row r="22" spans="1:44" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="M22" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="O22" s="70"/>
-      <c r="P22" s="50"/>
-      <c r="Q22" s="50"/>
-      <c r="R22" s="51"/>
-      <c r="S22" s="74"/>
-      <c r="T22" s="57"/>
-      <c r="U22" s="70" t="s">
+      <c r="O22" s="21"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22"/>
+      <c r="R22" s="23"/>
+      <c r="S22" s="24"/>
+      <c r="T22" s="25"/>
+      <c r="U22" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="V22" s="50"/>
-      <c r="W22" s="51"/>
+      <c r="V22" s="22"/>
+      <c r="W22" s="23"/>
     </row>
     <row r="23" spans="1:44" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
-      <c r="N23" s="17"/>
-      <c r="O23" s="17"/>
-      <c r="P23" s="17"/>
-      <c r="Q23" s="17"/>
-      <c r="R23" s="17"/>
-      <c r="S23" s="17"/>
-      <c r="T23" s="17"/>
-      <c r="U23" s="17"/>
-      <c r="V23" s="17"/>
-      <c r="W23" s="17"/>
-      <c r="X23" s="17"/>
-      <c r="Y23" s="17"/>
-      <c r="Z23" s="17"/>
-      <c r="AA23" s="17"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
+      <c r="R23" s="20"/>
+      <c r="S23" s="20"/>
+      <c r="T23" s="20"/>
+      <c r="U23" s="20"/>
+      <c r="V23" s="20"/>
+      <c r="W23" s="20"/>
+      <c r="X23" s="20"/>
+      <c r="Y23" s="20"/>
+      <c r="Z23" s="20"/>
+      <c r="AA23" s="20"/>
     </row>
     <row r="24" spans="1:44" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="N24" s="14" t="s">
+      <c r="N24" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="O24" s="17"/>
-      <c r="P24" s="17"/>
-      <c r="Q24" s="17"/>
-      <c r="R24" s="17"/>
-      <c r="S24" s="17"/>
-      <c r="T24" s="17"/>
-      <c r="U24" s="17"/>
-      <c r="V24" s="17"/>
-      <c r="W24" s="17"/>
-      <c r="X24" s="17"/>
-      <c r="Y24" s="17"/>
-      <c r="Z24" s="17"/>
-      <c r="AA24" s="17"/>
-      <c r="AB24" s="17"/>
-      <c r="AC24" s="17"/>
-      <c r="AD24" s="17"/>
-      <c r="AE24" s="17"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
+      <c r="R24" s="20"/>
+      <c r="S24" s="20"/>
+      <c r="T24" s="20"/>
+      <c r="U24" s="20"/>
+      <c r="V24" s="20"/>
+      <c r="W24" s="20"/>
+      <c r="X24" s="20"/>
+      <c r="Y24" s="20"/>
+      <c r="Z24" s="20"/>
+      <c r="AA24" s="20"/>
+      <c r="AB24" s="20"/>
+      <c r="AC24" s="20"/>
+      <c r="AD24" s="20"/>
+      <c r="AE24" s="20"/>
     </row>
     <row r="25" spans="1:44" ht="5.85" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="26" spans="1:44" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B26" s="71" t="s">
+      <c r="B26" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="17"/>
-      <c r="E26" s="72" t="s">
+      <c r="C26" s="20"/>
+      <c r="E26" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
-      <c r="M26" s="17"/>
-      <c r="N26" s="17"/>
-      <c r="O26" s="17"/>
-      <c r="Q26" s="71" t="s">
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="Q26" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="R26" s="17"/>
-      <c r="S26" s="17"/>
-      <c r="V26" s="72" t="s">
+      <c r="R26" s="20"/>
+      <c r="S26" s="20"/>
+      <c r="V26" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="W26" s="17"/>
-      <c r="X26" s="17"/>
-      <c r="Y26" s="17"/>
-      <c r="Z26" s="17"/>
-      <c r="AA26" s="17"/>
-      <c r="AB26" s="17"/>
-      <c r="AE26" s="71"/>
-      <c r="AF26" s="17"/>
-      <c r="AG26" s="17"/>
-      <c r="AJ26" s="72"/>
-      <c r="AK26" s="73"/>
-      <c r="AL26" s="73"/>
-      <c r="AM26" s="73"/>
-      <c r="AN26" s="73"/>
-      <c r="AO26" s="73"/>
-      <c r="AP26" s="73"/>
-      <c r="AQ26" s="73"/>
-      <c r="AR26" s="73"/>
+      <c r="W26" s="20"/>
+      <c r="X26" s="20"/>
+      <c r="Y26" s="20"/>
+      <c r="Z26" s="20"/>
+      <c r="AA26" s="20"/>
+      <c r="AB26" s="20"/>
+      <c r="AE26" s="18"/>
+      <c r="AF26" s="20"/>
+      <c r="AG26" s="20"/>
+      <c r="AJ26" s="19"/>
+      <c r="AK26" s="17"/>
+      <c r="AL26" s="17"/>
+      <c r="AM26" s="17"/>
+      <c r="AN26" s="17"/>
+      <c r="AO26" s="17"/>
+      <c r="AP26" s="17"/>
+      <c r="AQ26" s="17"/>
+      <c r="AR26" s="17"/>
     </row>
     <row r="27" spans="1:44" ht="5.85" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="17"/>
-      <c r="N27" s="17"/>
-      <c r="O27" s="17"/>
-      <c r="V27" s="17"/>
-      <c r="W27" s="17"/>
-      <c r="X27" s="17"/>
-      <c r="Y27" s="17"/>
-      <c r="Z27" s="17"/>
-      <c r="AA27" s="17"/>
-      <c r="AB27" s="17"/>
-      <c r="AJ27" s="73"/>
-      <c r="AK27" s="73"/>
-      <c r="AL27" s="73"/>
-      <c r="AM27" s="73"/>
-      <c r="AN27" s="73"/>
-      <c r="AO27" s="73"/>
-      <c r="AP27" s="73"/>
-      <c r="AQ27" s="73"/>
-      <c r="AR27" s="73"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
+      <c r="V27" s="20"/>
+      <c r="W27" s="20"/>
+      <c r="X27" s="20"/>
+      <c r="Y27" s="20"/>
+      <c r="Z27" s="20"/>
+      <c r="AA27" s="20"/>
+      <c r="AB27" s="20"/>
+      <c r="AJ27" s="17"/>
+      <c r="AK27" s="17"/>
+      <c r="AL27" s="17"/>
+      <c r="AM27" s="17"/>
+      <c r="AN27" s="17"/>
+      <c r="AO27" s="17"/>
+      <c r="AP27" s="17"/>
+      <c r="AQ27" s="17"/>
+      <c r="AR27" s="17"/>
     </row>
     <row r="28" spans="1:44" ht="5.85" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="29" spans="1:44" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B29" s="71" t="s">
+      <c r="B29" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="73"/>
-      <c r="E29" s="72" t="s">
+      <c r="C29" s="17"/>
+      <c r="E29" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F29" s="73"/>
-      <c r="G29" s="73"/>
-      <c r="H29" s="73"/>
-      <c r="I29" s="73"/>
-      <c r="J29" s="73"/>
-      <c r="K29" s="73"/>
-      <c r="L29" s="73"/>
-      <c r="M29" s="73"/>
-      <c r="N29" s="73"/>
-      <c r="O29" s="73"/>
-      <c r="Q29" s="71"/>
-      <c r="R29" s="73"/>
-      <c r="S29" s="73"/>
-      <c r="V29" s="72"/>
-      <c r="W29" s="73"/>
-      <c r="X29" s="73"/>
-      <c r="Y29" s="73"/>
-      <c r="Z29" s="73"/>
-      <c r="AA29" s="73"/>
-      <c r="AB29" s="73"/>
-      <c r="AD29" s="71"/>
-      <c r="AE29" s="73"/>
-      <c r="AF29" s="73"/>
-      <c r="AG29" s="73"/>
-      <c r="AJ29" s="72"/>
-      <c r="AK29" s="73"/>
-      <c r="AL29" s="73"/>
-      <c r="AM29" s="73"/>
-      <c r="AN29" s="73"/>
-      <c r="AO29" s="73"/>
-      <c r="AP29" s="73"/>
-      <c r="AQ29" s="73"/>
-      <c r="AR29" s="73"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="Q29" s="18"/>
+      <c r="R29" s="17"/>
+      <c r="S29" s="17"/>
+      <c r="V29" s="19"/>
+      <c r="W29" s="17"/>
+      <c r="X29" s="17"/>
+      <c r="Y29" s="17"/>
+      <c r="Z29" s="17"/>
+      <c r="AA29" s="17"/>
+      <c r="AB29" s="17"/>
+      <c r="AD29" s="18"/>
+      <c r="AE29" s="17"/>
+      <c r="AF29" s="17"/>
+      <c r="AG29" s="17"/>
+      <c r="AJ29" s="19"/>
+      <c r="AK29" s="17"/>
+      <c r="AL29" s="17"/>
+      <c r="AM29" s="17"/>
+      <c r="AN29" s="17"/>
+      <c r="AO29" s="17"/>
+      <c r="AP29" s="17"/>
+      <c r="AQ29" s="17"/>
+      <c r="AR29" s="17"/>
     </row>
     <row r="30" spans="1:44" ht="5.85" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E30" s="73"/>
-      <c r="F30" s="73"/>
-      <c r="G30" s="73"/>
-      <c r="H30" s="73"/>
-      <c r="I30" s="73"/>
-      <c r="J30" s="73"/>
-      <c r="K30" s="73"/>
-      <c r="L30" s="73"/>
-      <c r="M30" s="73"/>
-      <c r="N30" s="73"/>
-      <c r="O30" s="73"/>
-      <c r="V30" s="73"/>
-      <c r="W30" s="73"/>
-      <c r="X30" s="73"/>
-      <c r="Y30" s="73"/>
-      <c r="Z30" s="73"/>
-      <c r="AA30" s="73"/>
-      <c r="AB30" s="73"/>
-      <c r="AJ30" s="73"/>
-      <c r="AK30" s="73"/>
-      <c r="AL30" s="73"/>
-      <c r="AM30" s="73"/>
-      <c r="AN30" s="73"/>
-      <c r="AO30" s="73"/>
-      <c r="AP30" s="73"/>
-      <c r="AQ30" s="73"/>
-      <c r="AR30" s="73"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="V30" s="17"/>
+      <c r="W30" s="17"/>
+      <c r="X30" s="17"/>
+      <c r="Y30" s="17"/>
+      <c r="Z30" s="17"/>
+      <c r="AA30" s="17"/>
+      <c r="AB30" s="17"/>
+      <c r="AJ30" s="17"/>
+      <c r="AK30" s="17"/>
+      <c r="AL30" s="17"/>
+      <c r="AM30" s="17"/>
+      <c r="AN30" s="17"/>
+      <c r="AO30" s="17"/>
+      <c r="AP30" s="17"/>
+      <c r="AQ30" s="17"/>
+      <c r="AR30" s="17"/>
     </row>
     <row r="31" spans="1:44" ht="2.85" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="32" spans="1:44" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I32" s="81"/>
-      <c r="J32" s="73"/>
-      <c r="K32" s="73"/>
-      <c r="L32" s="73"/>
-      <c r="M32" s="73"/>
-      <c r="N32" s="73"/>
-      <c r="O32" s="73"/>
-      <c r="P32" s="73"/>
-      <c r="Q32" s="73"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="17"/>
+      <c r="M32" s="17"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="17"/>
+      <c r="Q32" s="17"/>
     </row>
     <row r="33" spans="2:20" ht="0.6" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="34" spans="2:20" s="5" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="8" t="s">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G34" s="9"/>
-      <c r="H34" s="10" t="s">
+      <c r="G34" s="7"/>
+      <c r="H34" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="12"/>
-      <c r="M34" s="12"/>
-      <c r="N34" s="12"/>
-      <c r="O34" s="11">
+      <c r="I34" s="76"/>
+      <c r="J34" s="76"/>
+      <c r="K34" s="76"/>
+      <c r="L34" s="76"/>
+      <c r="M34" s="76"/>
+      <c r="N34" s="76"/>
+      <c r="O34" s="9">
         <v>20</v>
       </c>
-      <c r="P34" s="13"/>
-      <c r="Q34" s="13"/>
-      <c r="R34" s="7" t="s">
+      <c r="P34" s="77"/>
+      <c r="Q34" s="77"/>
+      <c r="R34" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="S34" s="7"/>
-      <c r="T34" s="7"/>
-    </row>
-    <row r="35" spans="2:20" s="5" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="7"/>
-      <c r="M35" s="7"/>
-      <c r="N35" s="7"/>
-      <c r="O35" s="7"/>
-      <c r="P35" s="7"/>
-      <c r="Q35" s="7"/>
-      <c r="R35" s="7"/>
-      <c r="S35" s="7"/>
-      <c r="T35" s="7"/>
-    </row>
-    <row r="36" spans="2:20" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="37" spans="2:20" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="38" spans="2:20" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="39" spans="2:20" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="40" spans="2:20" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="41" spans="2:20" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="42" spans="2:20" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="43" spans="2:20" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="44" spans="2:20" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="45" spans="2:20" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="46" spans="2:20" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="47" spans="2:20" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="48" spans="2:20" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="49" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="50" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="51" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="52" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="53" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="54" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="55" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="56" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="57" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="58" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="59" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="60" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="61" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="62" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="63" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="64" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="65" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="66" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="67" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="68" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="69" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="70" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="71" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="72" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="73" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="74" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="75" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="76" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="77" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="78" s="5" customFormat="1" x14ac:dyDescent="0.45"/>
+      <c r="S34" s="5"/>
+      <c r="T34" s="5"/>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5"/>
+      <c r="R35" s="5"/>
+      <c r="S35" s="5"/>
+      <c r="T35" s="5"/>
+    </row>
+    <row r="49" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="50" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="51" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="52" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="53" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="54" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="55" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="56" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="57" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="58" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="59" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="60" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="61" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="62" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="63" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="64" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="65" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="66" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="67" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="68" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="69" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="70" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="71" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="72" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="73" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="74" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="75" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="76" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="77" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="78" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
     <row r="81" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
     <row r="82" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
     <row r="83" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
@@ -2621,6 +2575,60 @@
     <row r="99" s="3" customFormat="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="70">
+    <mergeCell ref="I34:N34"/>
+    <mergeCell ref="P34:Q34"/>
+    <mergeCell ref="A6:E8"/>
+    <mergeCell ref="A12:E14"/>
+    <mergeCell ref="A10:E11"/>
+    <mergeCell ref="F10:X11"/>
+    <mergeCell ref="A15:E16"/>
+    <mergeCell ref="A17:E18"/>
+    <mergeCell ref="F17:X18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="G1:AF1"/>
+    <mergeCell ref="AK1:AR2"/>
+    <mergeCell ref="G2:AF2"/>
+    <mergeCell ref="G3:AF4"/>
+    <mergeCell ref="AO4:AR5"/>
+    <mergeCell ref="AQ8:AQ10"/>
+    <mergeCell ref="AR8:AR10"/>
+    <mergeCell ref="AM9:AM11"/>
+    <mergeCell ref="AO11:AR12"/>
+    <mergeCell ref="F12:X14"/>
+    <mergeCell ref="AO13:AR15"/>
+    <mergeCell ref="F15:X16"/>
+    <mergeCell ref="AO16:AR16"/>
+    <mergeCell ref="AM12:AM14"/>
+    <mergeCell ref="F6:V8"/>
+    <mergeCell ref="W6:AK8"/>
+    <mergeCell ref="AM6:AM8"/>
+    <mergeCell ref="AO6:AR7"/>
+    <mergeCell ref="AO8:AP10"/>
+    <mergeCell ref="AO17:AR17"/>
+    <mergeCell ref="C19:I19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="O19:R19"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="U19:W19"/>
+    <mergeCell ref="AI19:AO19"/>
+    <mergeCell ref="AP19:AR19"/>
+    <mergeCell ref="AP20:AR21"/>
+    <mergeCell ref="A20:B21"/>
+    <mergeCell ref="C20:I21"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="L20:N21"/>
+    <mergeCell ref="O20:R21"/>
+    <mergeCell ref="S20:T21"/>
+    <mergeCell ref="U20:W21"/>
+    <mergeCell ref="X20:Y21"/>
+    <mergeCell ref="Z20:Z21"/>
+    <mergeCell ref="AA20:AH21"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="AA19:AH19"/>
+    <mergeCell ref="Q26:S26"/>
+    <mergeCell ref="V26:AB27"/>
+    <mergeCell ref="AE26:AG26"/>
     <mergeCell ref="AI20:AO21"/>
     <mergeCell ref="I32:Q32"/>
     <mergeCell ref="B29:C29"/>
@@ -2637,60 +2645,6 @@
     <mergeCell ref="U22:W22"/>
     <mergeCell ref="B23:AA23"/>
     <mergeCell ref="N24:AE24"/>
-    <mergeCell ref="Z20:Z21"/>
-    <mergeCell ref="AA20:AH21"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="AA19:AH19"/>
-    <mergeCell ref="Q26:S26"/>
-    <mergeCell ref="V26:AB27"/>
-    <mergeCell ref="AE26:AG26"/>
-    <mergeCell ref="AP20:AR21"/>
-    <mergeCell ref="A20:B21"/>
-    <mergeCell ref="C20:I21"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="K20:K21"/>
-    <mergeCell ref="L20:N21"/>
-    <mergeCell ref="O20:R21"/>
-    <mergeCell ref="S20:T21"/>
-    <mergeCell ref="U20:W21"/>
-    <mergeCell ref="X20:Y21"/>
-    <mergeCell ref="AO17:AR17"/>
-    <mergeCell ref="C19:I19"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="O19:R19"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="U19:W19"/>
-    <mergeCell ref="AI19:AO19"/>
-    <mergeCell ref="AP19:AR19"/>
-    <mergeCell ref="AQ8:AQ10"/>
-    <mergeCell ref="AR8:AR10"/>
-    <mergeCell ref="AM9:AM11"/>
-    <mergeCell ref="AO11:AR12"/>
-    <mergeCell ref="F12:X14"/>
-    <mergeCell ref="AO13:AR15"/>
-    <mergeCell ref="F15:X16"/>
-    <mergeCell ref="AO16:AR16"/>
-    <mergeCell ref="AM12:AM14"/>
-    <mergeCell ref="G1:AF1"/>
-    <mergeCell ref="AK1:AR2"/>
-    <mergeCell ref="G2:AF2"/>
-    <mergeCell ref="G3:AF4"/>
-    <mergeCell ref="AO4:AR5"/>
-    <mergeCell ref="F6:V8"/>
-    <mergeCell ref="W6:AK8"/>
-    <mergeCell ref="AM6:AM8"/>
-    <mergeCell ref="AO6:AR7"/>
-    <mergeCell ref="AO8:AP10"/>
-    <mergeCell ref="I34:N34"/>
-    <mergeCell ref="P34:Q34"/>
-    <mergeCell ref="A6:E8"/>
-    <mergeCell ref="A12:E14"/>
-    <mergeCell ref="A10:E11"/>
-    <mergeCell ref="F10:X11"/>
-    <mergeCell ref="A15:E16"/>
-    <mergeCell ref="A17:E18"/>
-    <mergeCell ref="F17:X18"/>
-    <mergeCell ref="A19:B19"/>
   </mergeCells>
   <pageMargins left="0.3611111111111111" right="0.3611111111111111" top="0.3611111111111111" bottom="0.3611111111111111" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
